--- a/tests/fixtures/sumprod.xlsx
+++ b/tests/fixtures/sumprod.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391238E7-C035-465A-9E30-ECC3655A72D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89ADDFA4-6458-43FB-BA70-C3F4050B5463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="3120" windowWidth="28800" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data1" sheetId="1" r:id="rId1"/>
     <sheet name="qrtr" sheetId="2" r:id="rId2"/>
     <sheet name="rolly" sheetId="3" r:id="rId3"/>
+    <sheet name="data2" sheetId="4" r:id="rId4"/>
+    <sheet name="concepts_adds" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="55">
   <si>
     <t>entity</t>
   </si>
@@ -97,6 +99,96 @@
   </si>
   <si>
     <t>idx</t>
+  </si>
+  <si>
+    <t>EBITDA</t>
+  </si>
+  <si>
+    <t>TangibleAssetsNoncash</t>
+  </si>
+  <si>
+    <t>qrtr</t>
+  </si>
+  <si>
+    <t>concept_add</t>
+  </si>
+  <si>
+    <t>concept_from</t>
+  </si>
+  <si>
+    <t>fstype</t>
+  </si>
+  <si>
+    <t>coef</t>
+  </si>
+  <si>
+    <t>AssetsNongoodwillNoncash</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>bs</t>
+  </si>
+  <si>
+    <t>DebtBearingInterest</t>
+  </si>
+  <si>
+    <t>BankOverDrafts</t>
+  </si>
+  <si>
+    <t>DebtBearingInterestEquity</t>
+  </si>
+  <si>
+    <t>DebtBearingInterestShares</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>CashAndCashEquivalents</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>Goodwill</t>
+  </si>
+  <si>
+    <t>IntangibleAssetsNetExcludingGoodwill</t>
+  </si>
+  <si>
+    <t>LongTermDebtAndLeaseObligations</t>
+  </si>
+  <si>
+    <t>LongTermDebtAndLeaseObligationsCurrent</t>
+  </si>
+  <si>
+    <t>ShareCapital</t>
+  </si>
+  <si>
+    <t>FixedCosts</t>
+  </si>
+  <si>
+    <t>AdministrationActivities</t>
+  </si>
+  <si>
+    <t>is</t>
+  </si>
+  <si>
+    <t>EbitdaExclUnusalAndExtraordinary</t>
+  </si>
+  <si>
+    <t>FixedProduction</t>
+  </si>
+  <si>
+    <t>OperatingActivities</t>
+  </si>
+  <si>
+    <t>SellingActivities</t>
+  </si>
+  <si>
+    <t>UnusualGainsLosses</t>
   </si>
 </sst>
 </file>
@@ -132,7 +224,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,6 +273,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -210,7 +314,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -233,6 +337,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -249,6 +360,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D7EFAE3-F87F-4064-85C3-9BBC1CE4994A}" name="concepts_adds" displayName="concepts_adds" ref="A1:D27" totalsRowShown="0">
+  <autoFilter ref="A1:D27" xr:uid="{5D7EFAE3-F87F-4064-85C3-9BBC1CE4994A}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="DebtBearingInterest"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{412D6112-857C-4CBE-9800-D1870FF2BA72}" name="concept_add"/>
+    <tableColumn id="2" xr3:uid="{FC770A68-4966-4AB5-A624-4B95C294D977}" name="concept_from"/>
+    <tableColumn id="3" xr3:uid="{B535511B-AC74-4091-831D-AC01DFEF237A}" name="fstype"/>
+    <tableColumn id="4" xr3:uid="{2402D9C5-6A76-4662-BBF4-381D73B61B32}" name="coef"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1740,4 +1870,888 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9270AD74-9F73-4357-B57D-6F0DD58F65BB}">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D2,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3">
+        <v>150</v>
+      </c>
+      <c r="F3" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D3,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D4,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5">
+        <v>200</v>
+      </c>
+      <c r="F5" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D5,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>150</v>
+      </c>
+      <c r="F6" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D6,concepts_adds[concept_from],0))</f>
+        <v>EbitdaExclUnusalAndExtraordinary</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7">
+        <v>-10</v>
+      </c>
+      <c r="F7" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D7,concepts_adds[concept_from],0))</f>
+        <v>EbitdaExclUnusalAndExtraordinary</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>125</v>
+      </c>
+      <c r="F8" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D8,concepts_adds[concept_from],0))</f>
+        <v>EbitdaExclUnusalAndExtraordinary</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D9,concepts_adds[concept_from],0))</f>
+        <v>EbitdaExclUnusalAndExtraordinary</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10">
+        <v>1000</v>
+      </c>
+      <c r="F10" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D10,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11">
+        <v>150</v>
+      </c>
+      <c r="F11" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D11,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D12,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13">
+        <v>200</v>
+      </c>
+      <c r="F13" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D13,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14">
+        <v>1000</v>
+      </c>
+      <c r="F14" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D14,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D15,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D16,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17">
+        <v>200</v>
+      </c>
+      <c r="F17" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D17,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D18,concepts_adds[concept_from],0))</f>
+        <v>EbitdaExclUnusalAndExtraordinary</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19">
+        <v>-10</v>
+      </c>
+      <c r="F19" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D19,concepts_adds[concept_from],0))</f>
+        <v>EbitdaExclUnusalAndExtraordinary</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20">
+        <v>1000</v>
+      </c>
+      <c r="F20" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D20,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21">
+        <v>150</v>
+      </c>
+      <c r="F21" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D21,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22">
+        <v>50</v>
+      </c>
+      <c r="F22" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D22,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23">
+        <v>200</v>
+      </c>
+      <c r="F23" t="str">
+        <f>INDEX(concepts_adds[concept_add], MATCH(D23,concepts_adds[concept_from],0))</f>
+        <v>AssetsNongoodwillNoncash</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2686EF9-13CF-446E-BDAB-47D3A486AC54}">
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="40.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/tests/fixtures/sumprod.xlsx
+++ b/tests/fixtures/sumprod.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89ADDFA4-6458-43FB-BA70-C3F4050B5463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A964C2C2-3D5C-44C2-9B03-4425D842302C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="3120" windowWidth="28800" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="3120" windowWidth="28800" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data1" sheetId="1" r:id="rId1"/>
@@ -364,13 +364,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D7EFAE3-F87F-4064-85C3-9BBC1CE4994A}" name="concepts_adds" displayName="concepts_adds" ref="A1:D27" totalsRowShown="0">
-  <autoFilter ref="A1:D27" xr:uid="{5D7EFAE3-F87F-4064-85C3-9BBC1CE4994A}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="DebtBearingInterest"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D27" xr:uid="{5D7EFAE3-F87F-4064-85C3-9BBC1CE4994A}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{412D6112-857C-4CBE-9800-D1870FF2BA72}" name="concept_add"/>
     <tableColumn id="2" xr3:uid="{FC770A68-4966-4AB5-A624-4B95C294D977}" name="concept_from"/>
@@ -2384,7 +2378,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -2398,7 +2392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -2426,7 +2420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2440,7 +2434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -2454,7 +2448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -2468,7 +2462,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -2482,7 +2476,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -2496,7 +2490,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2510,7 +2504,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -2524,7 +2518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -2538,7 +2532,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -2552,7 +2546,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2580,7 +2574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -2594,7 +2588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -2622,7 +2616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -2636,7 +2630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -2650,7 +2644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -2664,7 +2658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -2678,7 +2672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -2692,7 +2686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -2706,7 +2700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -2720,7 +2714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -2734,7 +2728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>50</v>
       </c>

--- a/tests/fixtures/sumprod.xlsx
+++ b/tests/fixtures/sumprod.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A964C2C2-3D5C-44C2-9B03-4425D842302C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C560B14D-D045-4165-9DC1-73F6B5CCD1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="3120" windowWidth="28800" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="3120" windowWidth="28800" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="56">
   <si>
     <t>entity</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>UnusualGainsLosses</t>
+  </si>
+  <si>
+    <t>concept_total</t>
   </si>
 </sst>
 </file>
@@ -1882,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>1</v>
@@ -1894,7 +1897,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
